--- a/RSA analysis/excluded_subs_hammer.xlsx
+++ b/RSA analysis/excluded_subs_hammer.xlsx
@@ -532,7 +532,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -544,7 +544,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -556,7 +556,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -580,7 +580,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -592,7 +592,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -726,7 +726,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -738,7 +738,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -774,7 +774,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -786,7 +786,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -798,7 +798,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -944,7 +944,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -968,7 +968,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -992,7 +992,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1078,7 +1078,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1090,7 +1090,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1114,7 +1114,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1138,7 +1138,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1150,7 +1150,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1284,7 +1284,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1308,7 +1308,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1320,7 +1320,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1356,7 +1356,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1368,7 +1368,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1502,7 +1502,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1514,7 +1514,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1526,7 +1526,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1538,7 +1538,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1550,7 +1550,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1562,7 +1562,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1574,7 +1574,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/RSA analysis/excluded_subs_hammer.xlsx
+++ b/RSA analysis/excluded_subs_hammer.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (40) exceeds 20% of series length after interpolation(73)</t>
+          <t>Interpolated ibis count (33) exceeds 20% of series length after interpolation(69)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -544,7 +544,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -556,7 +556,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -568,7 +568,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -580,7 +580,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -592,7 +592,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -726,7 +726,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -738,7 +738,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -774,7 +774,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -786,7 +786,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -798,7 +798,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -920,7 +920,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -944,7 +944,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -968,7 +968,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -992,7 +992,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1078,7 +1078,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1090,7 +1090,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1114,7 +1114,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1138,7 +1138,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1284,7 +1284,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1308,7 +1308,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1332,7 +1332,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1356,7 +1356,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1368,7 +1368,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1502,7 +1502,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1514,7 +1514,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1526,7 +1526,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1538,7 +1538,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1550,7 +1550,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1574,7 +1574,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1586,7 +1586,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">

--- a/RSA analysis/excluded_subs_hammer.xlsx
+++ b/RSA analysis/excluded_subs_hammer.xlsx
@@ -520,7 +520,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -532,7 +532,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -556,7 +556,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -568,7 +568,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -580,7 +580,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -592,7 +592,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -726,7 +726,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -774,7 +774,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -786,7 +786,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -798,7 +798,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -920,7 +920,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -944,7 +944,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -968,7 +968,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -992,7 +992,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1090,7 +1090,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1114,7 +1114,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1138,7 +1138,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1150,7 +1150,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1284,7 +1284,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1308,7 +1308,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1320,7 +1320,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1332,7 +1332,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1356,7 +1356,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1368,7 +1368,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1380,7 +1380,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1514,7 +1514,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1526,7 +1526,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1538,7 +1538,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1550,7 +1550,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1562,7 +1562,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1574,7 +1574,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1586,7 +1586,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
